--- a/output/2026-09-05_14_Italia_Sicilia_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-05_14_Italia_Sicilia_Componentistica_Ventilazione_industriale.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Esistenza confermata su directory di settore (categoria "Aspiratori" su Guida Sicilia; presente anche su Pagine Gialle/Bianche). Indirizzo: Via Uditore 14/L, 90145 Palermo.</t>
+          <t>Esistenza confermata su directory di settore (categoria "Aspiratori" su Guida Sicilia; presente anche su Pagine Gialle/Bianche). Indirizzo: Via Uditore 14/L, 90145 Palermo. [DUPLICATO — vedi anche: 2026-09-05_12_Italia_Sicilia_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
